--- a/マニュアル.xlsx
+++ b/マニュアル.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\7032_川井\SR案件①_20240125\kintone_plugin_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B033B58E-E814-479C-8E4F-DD06D14A46AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A7A159-C42D-4E90-B72F-6F506B457E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="18490" windowHeight="11020" xr2:uid="{B4F1298A-2663-45A2-839A-C90A82757019}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="01.fieldConf" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$H$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'01.fieldConf'!$A$1:$L$60</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="67">
   <si>
     <t>window</t>
     <phoneticPr fontId="1"/>
@@ -42,102 +42,589 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>field</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フィールドコード(任意のキー)</t>
-    <rPh sb="9" eb="11">
+    <t>settings</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>label</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>""</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>requiredIcon</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>value</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>placeholder</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>prefix</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>suffix</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>textAlign</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>error</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>className</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>visible</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>disabled</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>false</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>true</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"text"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"text-id"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>category</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"common"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FIELDS_CONFIG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>divId</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>text</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>任意のキー</t>
+    <rPh sb="0" eb="2">
       <t>ニンイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>settings</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>label</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>""</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>requiredIcon</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>value</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>placeholder</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>prefix</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>suffix</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>textAlign</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>error</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>className</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>visible</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>disabled</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>false</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>true</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>type</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>"text"</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>spaceId</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>"text-id"</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>category</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>"common"</t>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オブジェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（必須アイコン）</t>
+    </r>
+  </si>
+  <si>
+    <t>説明</t>
+    <rPh sb="0" eb="2">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本資料では、フィールドタイプごとの設定を記載しているため、フィールドタイプ名をキーとしている。</t>
+    <rPh sb="0" eb="3">
+      <t>ホンシリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目設定</t>
+    <rPh sb="0" eb="4">
+      <t>コウモクセッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィールド名や説明ラベルとして利用</t>
+    <rPh sb="5" eb="6">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>リヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>公式サイトのプロパティと同様。</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+https://ui-component.kintone.dev/ja/docs/components/desktop/text#property</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>コウシキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ドウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>値</t>
+    <rPh sb="0" eb="1">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未指定("")の場合、非表示。</t>
+    <rPh sb="0" eb="3">
+      <t>ミシテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ヒヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>型</t>
+    <rPh sb="0" eb="1">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>boolean</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未指定("")の場合、非表示。
+初期値を追加したい場合のみ、記載。</t>
+    <rPh sb="0" eb="3">
+      <t>ミシテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ヒヒョウジ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空欄時の入力例</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>値の先頭に表示されるテキスト</t>
+    <rPh sb="0" eb="1">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>値の後尾に表示されるテキスト</t>
+    <rPh sb="0" eb="1">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウビ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示するテキストの位置</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>trueの時、表示。falseの時、非表示。未指定の場合、false。
+アイコン表示のみのため、別途入力制御が必要。</t>
+  </si>
+  <si>
+    <t>未指定("")の場合、空。</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未指定("")の場合、値のみ。</t>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下のみ指定可能。未指定("")の場合、左寄せ。
+"left" : 左寄せ
+"right" : 右寄せ</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>シテイカノウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒダリヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィールドの下に表示するエラーテキスト</t>
+    <rPh sb="6" eb="7">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未指定("")の場合、非表示。
+event.フィールドコード.errorと同様の表示。
+表示のみのため、別途入力制御が必要。</t>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ヒヒョウジ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ベット</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンポーネントのクラス名</t>
+    <rPh sb="11" eb="12">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンポーネントのID名</t>
+    <rPh sb="10" eb="11">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必須</t>
+    <rPh sb="0" eb="2">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>任意</t>
+    <rPh sb="0" eb="2">
+      <t>ニンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>保存時の値取得のため等に必要なため、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>任意のid名を必ず設定すること。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンポーネントの表示/非表示</t>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ヒヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未指定の場合、true（表示）。</t>
+    <rPh sb="4" eb="6">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンポーネントの編集可否</t>
+    <rPh sb="8" eb="10">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未指定の場合、false（編集可）。</t>
+    <rPh sb="4" eb="6">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ヘンシュウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィールドタイプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示先のhtml&lt;div&gt;ID名</t>
+    <rPh sb="2" eb="3">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>任意のdiv idを記載。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>必ずhtml内に記載したidと合致する事。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するタイプを記載。
+テキストの場合、"text"。</t>
+    </r>
+    <rPh sb="30" eb="32">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するカテゴリーを記載。
+テキストの場合、"common"。</t>
+    </r>
+    <rPh sb="32" eb="34">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィールドカテゴリ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -145,7 +632,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,8 +648,86 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -175,8 +740,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -250,13 +821,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -293,8 +887,39 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -607,101 +1232,146 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86763921-03DB-411A-87EC-161042BDBDA7}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="5" max="5" width="27.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="3.9140625" customWidth="1"/>
+    <col min="4" max="4" width="5.5" customWidth="1"/>
+    <col min="5" max="5" width="6.5" customWidth="1"/>
     <col min="7" max="7" width="11.9140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.75" customWidth="1"/>
+    <col min="12" max="12" width="68.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="7"/>
-      <c r="B2" s="6" t="s">
-        <v>1</v>
-      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="6" t="s">
-        <v>2</v>
-      </c>
+      <c r="B3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="D5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+    </row>
+    <row r="6" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="F7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -709,13 +1379,25 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>4</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -723,13 +1405,25 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>6</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -737,13 +1431,25 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -751,13 +1457,25 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -765,13 +1483,25 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -779,13 +1509,25 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -793,13 +1535,25 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -807,13 +1561,25 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -821,13 +1587,23 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -835,71 +1611,163 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>14</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="5"/>
+      <c r="F18" s="4"/>
       <c r="G18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I18" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="9" t="s">
-        <v>21</v>
-      </c>
+      <c r="F19" s="5"/>
       <c r="G19" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H19" s="11"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>16</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="E20" s="4"/>
       <c r="F20" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H20" s="11"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="I20" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
       <c r="F21" s="9" t="s">
         <v>25</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H21" s="11"/>
+      <c r="I21" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="11"/>
+      <c r="I22" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>65</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="L7" r:id="rId1" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{13DE1523-B5FB-4FD9-A1B1-C0BF33C34386}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="12" scale="83" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/マニュアル.xlsx
+++ b/マニュアル.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\7032_川井\SR案件①_20240125\kintone_plugin_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A7A159-C42D-4E90-B72F-6F506B457E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9516A3A-850D-4E89-943B-70E8070E7499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="18490" windowHeight="11020" xr2:uid="{B4F1298A-2663-45A2-839A-C90A82757019}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="01.fieldConf" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'01.fieldConf'!$A$1:$L$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'01.fieldConf'!$A$1:$L$81</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="99">
   <si>
     <t>window</t>
     <phoneticPr fontId="1"/>
@@ -38,10 +38,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Conf</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>settings</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -111,10 +107,6 @@
   </si>
   <si>
     <t>"text"</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>"text-id"</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -186,22 +178,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>本資料では、フィールドタイプごとの設定を記載しているため、フィールドタイプ名をキーとしている。</t>
-    <rPh sb="0" eb="3">
-      <t>ホンシリョウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>キサイ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>項目設定</t>
     <rPh sb="0" eb="4">
       <t>コウモクセッテイ</t>
@@ -218,38 +194,6 @@
     </rPh>
     <rPh sb="15" eb="17">
       <t>リヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公式サイトのプロパティと同様。</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-https://ui-component.kintone.dev/ja/docs/components/desktop/text#property</t>
-    </r>
-    <rPh sb="0" eb="2">
-      <t>コウシキ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ドウヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -627,12 +571,470 @@
     <t>フィールドカテゴリ</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>fieldConf</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>textarea</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓文字列一行</t>
+    <rPh sb="1" eb="6">
+      <t>モジレツイチギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓文字列複数行</t>
+    <rPh sb="1" eb="4">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>div id名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"textarea"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>timePicker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E列は、あくまでも例。本資料では、フィールドタイプごとの設定を記載しているため、フィールドタイプ名をキーとしている。</t>
+    <rPh sb="1" eb="2">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ホンシリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E列は、あくまでも例。本資料では、フィールドタイプごとの設定を記載しているため、フィールドタイプ名をキーとしている。</t>
+    <rPh sb="11" eb="14">
+      <t>ホンシリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓時刻</t>
+    <rPh sb="1" eb="3">
+      <t>ジコク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hour12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期値</t>
+    <rPh sb="0" eb="3">
+      <t>ショキチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"left"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>公式サイトのプロパティと同様。※プロパティは省略可能。その場合、初期値が設定される。</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+https://ui-component.kintone.dev/ja/docs/components/desktop/text#property</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>コウシキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>ショウリャクカノウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>公式サイトのプロパティと同様。※プロパティは省略可能。その場合、初期値が設定される。</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+https://ui-component.kintone.dev/ja/docs/components/desktop/textarea#property</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>language</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>timeStep</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>max</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>min</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"auto"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>任意</t>
+  </si>
+  <si>
+    <t>number</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語設定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間間隔</t>
+    <rPh sb="0" eb="4">
+      <t>ジカンカンカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正の整数で、分単位で設定可能。max~minの時刻差異より大きい値の場合エラーとなる。</t>
+    <rPh sb="0" eb="1">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイスウ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>フンタンイ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>セッテイカノウ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>ジコクサイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終了時間指定</t>
+    <rPh sb="0" eb="4">
+      <t>シュウリョウジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開始時間指定</t>
+    <rPh sb="0" eb="2">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定した値(時刻)以降は表示されない。値は、"5:30"の通りに設定。</t>
+    <rPh sb="0" eb="2">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジコク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定した値(時刻)以前は表示されない。値は、"5:30"の通りに設定。</t>
+    <rPh sb="0" eb="2">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジコク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イゼン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"timePicker"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dateTimePicker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓日時</t>
+    <rPh sb="1" eb="3">
+      <t>ニチジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未指定("")の場合、非表示。初期値を追加したい場合のみ、記載。
+値は、YYYY-MM-DDTHH:MM:SSの通り、設定。
+月/日/時間/分/秒は省略可能。月日：01、時分秒：00として設定される。</t>
+    <rPh sb="0" eb="3">
+      <t>ミシテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ヒヒョウジ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ショウリャク</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>ツキヒ</t>
+    </rPh>
+    <rPh sb="85" eb="88">
+      <t>ジフンビョウ</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時刻表記</t>
+    <rPh sb="0" eb="2">
+      <t>ジコク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>true: 12時間表記
+false: 24時間表記（初期値）</t>
+    <rPh sb="27" eb="30">
+      <t>ショキチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未指定("")の場合、非表示。初期値を追加したい場合のみ、記載。
+値は、00:00の通り、設定。</t>
+    <rPh sb="0" eb="3">
+      <t>ミシテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ヒヒョウジ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -726,6 +1128,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -747,7 +1158,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -841,6 +1252,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -850,7 +1285,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -860,9 +1295,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -881,41 +1313,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1232,43 +1713,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86763921-03DB-411A-87EC-161042BDBDA7}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="3" width="3.9140625" customWidth="1"/>
     <col min="4" max="4" width="5.5" customWidth="1"/>
-    <col min="5" max="5" width="6.5" customWidth="1"/>
+    <col min="5" max="5" width="20.4140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.9140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="37"/>
+    <col min="9" max="9" width="5.1640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="21"/>
     <col min="11" max="11" width="26.75" customWidth="1"/>
     <col min="12" max="12" width="68.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J1" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>28</v>
+      <c r="L1" s="10" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2"/>
@@ -1277,15 +1763,15 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="7"/>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2"/>
@@ -1293,481 +1779,1696 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="6" t="s">
-        <v>2</v>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="6" t="s">
-        <v>24</v>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="16" t="s">
+        <v>22</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="16" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="23"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="1" t="s">
+      <c r="L10" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" s="8"/>
+    </row>
+    <row r="17" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="36"/>
+      <c r="I20" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" s="36"/>
+      <c r="I21" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="36"/>
+      <c r="I22" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="6"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="6"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="6"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="9" t="s">
+      <c r="H25" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L25" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="L7" s="17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="9" t="s">
+    </row>
+    <row r="26" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="6"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="6"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H27" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="I27" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="6"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="6"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="6"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L30" s="8"/>
+    </row>
+    <row r="31" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="6"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J31" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="6"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="6"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="6"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H34" s="36"/>
+      <c r="I34" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="6"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H35" s="36"/>
+      <c r="I35" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="6"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="36"/>
+      <c r="I36" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J36" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L36" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="6"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="6"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L38" s="13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="6"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H39" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L39" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="6"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="H40" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J40" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="6"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J41" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="6"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H42" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J42" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="6"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J43" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K43" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L43" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="6"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J44" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L44" s="8"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="6"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J45" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="6"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J46" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L46" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="6"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J47" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K47" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="9" t="s">
+      <c r="L47" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="6"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H48" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="I48" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J48" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L48" s="12"/>
+    </row>
+    <row r="49" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="6"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H49" s="35">
+        <v>30</v>
+      </c>
+      <c r="I49" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="J49" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L49" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="6"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H50" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="I50" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J50" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L50" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="6"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H51" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="I51" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J51" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L51" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="6"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H52" s="36"/>
+      <c r="I52" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J52" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L52" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="6"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H53" s="36"/>
+      <c r="I53" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J53" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="6"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H54" s="36"/>
+      <c r="I54" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J54" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L54" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="6"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="F55" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="G55" s="2"/>
+      <c r="H55" s="33"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L55" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="6"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G56" s="2"/>
+      <c r="H56" s="33"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L56" s="13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="6"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J57" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L57" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="6"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J58" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L58" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="6"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H59" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J59" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="L59" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="6"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H60" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J60" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L60" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="6"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I61" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J61" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K61" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L61" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="6"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H62" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J62" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L62" s="8"/>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="6"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I63" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J63" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="6"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H64" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J64" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L64" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="6"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J65" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L65" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="6"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H66" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="I66" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J66" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K66" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L66" s="12"/>
+    </row>
+    <row r="67" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="6"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H67" s="35">
+        <v>30</v>
+      </c>
+      <c r="I67" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="J67" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L67" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="6"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H68" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="I68" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J68" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K68" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L68" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="6"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H69" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="I69" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J69" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K69" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L69" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="6"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K15" s="16" t="s">
+      <c r="G70" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H70" s="36"/>
+      <c r="I70" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="L15" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="K18" s="9" t="s">
+      <c r="J70" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K70" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="L18" s="16" t="s">
+      <c r="L70" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="6"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H71" s="36"/>
+      <c r="I71" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J71" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K71" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="K19" s="9" t="s">
+      <c r="L71" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="L19" s="16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="9" t="s">
+    </row>
+    <row r="72" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="6"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K20" s="9" t="s">
+      <c r="G72" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H72" s="36"/>
+      <c r="I72" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J72" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K72" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L72" s="12" t="s">
         <v>61</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L22" s="16" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="L7" r:id="rId1" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{13DE1523-B5FB-4FD9-A1B1-C0BF33C34386}"/>
+    <hyperlink ref="L24" r:id="rId2" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{4E3AB564-235F-4DAA-AB2E-0A796A8F14FF}"/>
+    <hyperlink ref="L38" r:id="rId3" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{A5F7688D-101F-4607-9B37-CE23A225ADB1}"/>
+    <hyperlink ref="L56" r:id="rId4" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{6DF4276D-B532-4201-8152-E3F4BA2FAC53}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="12" scale="83" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="12" scale="61" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/マニュアル.xlsx
+++ b/マニュアル.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\7032_川井\SR案件①_20240125\kintone_plugin_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9516A3A-850D-4E89-943B-70E8070E7499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02ED0F4C-CDFE-4AD6-A604-BF7FD6233192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="18490" windowHeight="11020" xr2:uid="{B4F1298A-2663-45A2-839A-C90A82757019}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="102">
   <si>
     <t>window</t>
     <phoneticPr fontId="1"/>
@@ -1027,6 +1027,62 @@
     <rPh sb="45" eb="47">
       <t>セッテイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"dateTimePicker"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>公式サイトのプロパティと同様。※プロパティは省略可能。その場合、初期値が設定される。</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+https://ui-component.kintone.dev/ja/docs/components/desktop/time-picker#property</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>公式サイトのプロパティと同様。※プロパティは省略可能。その場合、初期値が設定される。</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+https://ui-component.kintone.dev/ja/docs/components/desktop/datetime-picker#property</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1285,7 +1341,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1331,9 +1387,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1354,18 +1407,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
@@ -1397,6 +1447,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1719,24 +1772,24 @@
     <col min="1" max="3" width="3.9140625" customWidth="1"/>
     <col min="4" max="4" width="5.5" customWidth="1"/>
     <col min="5" max="5" width="20.4140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.9140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="37"/>
-    <col min="9" max="9" width="5.1640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="21"/>
+    <col min="7" max="7" width="16.4140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="35"/>
+    <col min="9" max="9" width="5.1640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="20"/>
     <col min="11" max="11" width="26.75" customWidth="1"/>
     <col min="12" max="12" width="68.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
       <c r="H1" s="10" t="s">
         <v>74</v>
       </c>
@@ -1763,9 +1816,9 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
     </row>
@@ -1779,9 +1832,9 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
     </row>
@@ -1795,43 +1848,43 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="16" t="s">
+      <c r="C5" s="16"/>
+      <c r="D5" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="25" t="s">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
       <c r="K6" s="8" t="s">
         <v>25</v>
       </c>
@@ -1842,16 +1895,16 @@
     <row r="7" spans="1:12" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="26"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="24"/>
       <c r="F7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
       <c r="K7" s="8" t="s">
         <v>30</v>
       </c>
@@ -1862,20 +1915,20 @@
     <row r="8" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="24"/>
       <c r="F8" s="3"/>
       <c r="G8" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="H8" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="19" t="s">
+      <c r="I8" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K8" s="12" t="s">
@@ -1888,20 +1941,20 @@
     <row r="9" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="24"/>
       <c r="F9" s="3"/>
       <c r="G9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="22" t="s">
+      <c r="I9" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="21" t="s">
         <v>36</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -1914,20 +1967,20 @@
     <row r="10" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="26"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="24"/>
       <c r="F10" s="3"/>
       <c r="G10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="34" t="s">
+      <c r="H10" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" s="19" t="s">
+      <c r="I10" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K10" s="8" t="s">
@@ -1940,20 +1993,20 @@
     <row r="11" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="26"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="24"/>
       <c r="F11" s="3"/>
       <c r="G11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="34" t="s">
+      <c r="H11" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J11" s="19" t="s">
+      <c r="I11" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K11" s="8" t="s">
@@ -1966,20 +2019,20 @@
     <row r="12" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="24"/>
       <c r="F12" s="3"/>
       <c r="G12" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="34" t="s">
+      <c r="H12" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" s="19" t="s">
+      <c r="I12" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K12" s="8" t="s">
@@ -1992,20 +2045,20 @@
     <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="24"/>
       <c r="F13" s="3"/>
       <c r="G13" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="34" t="s">
+      <c r="H13" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J13" s="19" t="s">
+      <c r="I13" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K13" s="8" t="s">
@@ -2018,20 +2071,20 @@
     <row r="14" spans="1:12" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="26"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="24"/>
       <c r="F14" s="3"/>
       <c r="G14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="34" t="s">
+      <c r="H14" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="I14" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" s="19" t="s">
+      <c r="I14" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K14" s="8" t="s">
@@ -2044,20 +2097,20 @@
     <row r="15" spans="1:12" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="26"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="24"/>
       <c r="F15" s="3"/>
       <c r="G15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="34" t="s">
+      <c r="H15" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" s="19" t="s">
+      <c r="I15" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K15" s="12" t="s">
@@ -2070,20 +2123,20 @@
     <row r="16" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="26"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="24"/>
       <c r="F16" s="3"/>
       <c r="G16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="34" t="s">
+      <c r="H16" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J16" s="19" t="s">
+      <c r="I16" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K16" s="8" t="s">
@@ -2094,20 +2147,20 @@
     <row r="17" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="26"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="24"/>
       <c r="F17" s="3"/>
       <c r="G17" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="34" t="s">
+      <c r="H17" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I17" s="20" t="s">
+      <c r="I17" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J17" s="19" t="s">
+      <c r="J17" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K17" s="8" t="s">
@@ -2120,20 +2173,20 @@
     <row r="18" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="26"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="3"/>
       <c r="G18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="35" t="s">
+      <c r="H18" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J18" s="19" t="s">
+      <c r="I18" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" s="18" t="s">
         <v>36</v>
       </c>
       <c r="K18" s="8" t="s">
@@ -2146,20 +2199,20 @@
     <row r="19" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="26"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="24"/>
       <c r="F19" s="4"/>
       <c r="G19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="35" t="s">
+      <c r="H19" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="I19" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J19" s="19" t="s">
+      <c r="I19" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" s="18" t="s">
         <v>36</v>
       </c>
       <c r="K19" s="8" t="s">
@@ -2172,20 +2225,20 @@
     <row r="20" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="26"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="24"/>
       <c r="F20" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H20" s="36"/>
-      <c r="I20" s="20" t="s">
+      <c r="H20" s="34"/>
+      <c r="I20" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J20" s="19" t="s">
+      <c r="J20" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K20" s="8" t="s">
@@ -2198,20 +2251,20 @@
     <row r="21" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="27"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="25"/>
       <c r="F21" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H21" s="36"/>
-      <c r="I21" s="20" t="s">
+      <c r="H21" s="34"/>
+      <c r="I21" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K21" s="8" t="s">
@@ -2224,20 +2277,20 @@
     <row r="22" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="28"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="26"/>
       <c r="F22" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="20" t="s">
+      <c r="H22" s="34"/>
+      <c r="I22" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J22" s="19" t="s">
+      <c r="J22" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K22" s="8" t="s">
@@ -2249,18 +2302,18 @@
     </row>
     <row r="23" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="6"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="29" t="s">
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="22" t="s">
         <v>66</v>
       </c>
       <c r="G23" s="2"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
       <c r="K23" s="8" t="s">
         <v>25</v>
       </c>
@@ -2270,16 +2323,16 @@
     </row>
     <row r="24" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="6"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="30"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="28"/>
       <c r="F24" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G24" s="2"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
       <c r="K24" s="8" t="s">
         <v>30</v>
       </c>
@@ -2289,20 +2342,20 @@
     </row>
     <row r="25" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="6"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="30"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="28"/>
       <c r="F25" s="3"/>
       <c r="G25" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H25" s="34" t="s">
+      <c r="H25" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I25" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J25" s="19" t="s">
+      <c r="I25" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K25" s="12" t="s">
@@ -2314,20 +2367,20 @@
     </row>
     <row r="26" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="6"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="30"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="28"/>
       <c r="F26" s="3"/>
       <c r="G26" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H26" s="35" t="s">
+      <c r="H26" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J26" s="22" t="s">
+      <c r="I26" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J26" s="21" t="s">
         <v>36</v>
       </c>
       <c r="K26" s="11" t="s">
@@ -2339,20 +2392,20 @@
     </row>
     <row r="27" spans="1:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="6"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="30"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="28"/>
       <c r="F27" s="3"/>
       <c r="G27" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H27" s="34" t="s">
+      <c r="H27" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I27" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J27" s="19" t="s">
+      <c r="I27" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K27" s="8" t="s">
@@ -2364,20 +2417,20 @@
     </row>
     <row r="28" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="6"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="30"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="28"/>
       <c r="F28" s="3"/>
       <c r="G28" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="34" t="s">
+      <c r="H28" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I28" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J28" s="19" t="s">
+      <c r="I28" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J28" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K28" s="8" t="s">
@@ -2389,20 +2442,20 @@
     </row>
     <row r="29" spans="1:12" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="6"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="30"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="28"/>
       <c r="F29" s="3"/>
       <c r="G29" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H29" s="34" t="s">
+      <c r="H29" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J29" s="19" t="s">
+      <c r="I29" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J29" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K29" s="12" t="s">
@@ -2414,20 +2467,20 @@
     </row>
     <row r="30" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="6"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="30"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="28"/>
       <c r="F30" s="3"/>
       <c r="G30" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="34" t="s">
+      <c r="H30" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I30" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J30" s="19" t="s">
+      <c r="I30" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J30" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K30" s="8" t="s">
@@ -2437,20 +2490,20 @@
     </row>
     <row r="31" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="6"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="30"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="28"/>
       <c r="F31" s="3"/>
       <c r="G31" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H31" s="34" t="s">
+      <c r="H31" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I31" s="20" t="s">
+      <c r="I31" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J31" s="19" t="s">
+      <c r="J31" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K31" s="8" t="s">
@@ -2462,20 +2515,20 @@
     </row>
     <row r="32" spans="1:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="6"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="30"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="28"/>
       <c r="F32" s="3"/>
       <c r="G32" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="35" t="s">
+      <c r="H32" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="I32" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J32" s="19" t="s">
+      <c r="I32" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32" s="18" t="s">
         <v>36</v>
       </c>
       <c r="K32" s="8" t="s">
@@ -2487,20 +2540,20 @@
     </row>
     <row r="33" spans="2:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="6"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="30"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="28"/>
       <c r="F33" s="4"/>
       <c r="G33" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H33" s="35" t="s">
+      <c r="H33" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="I33" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J33" s="19" t="s">
+      <c r="I33" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J33" s="18" t="s">
         <v>36</v>
       </c>
       <c r="K33" s="8" t="s">
@@ -2512,20 +2565,20 @@
     </row>
     <row r="34" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="6"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="30"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="28"/>
       <c r="F34" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H34" s="36"/>
-      <c r="I34" s="20" t="s">
+      <c r="H34" s="34"/>
+      <c r="I34" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J34" s="19" t="s">
+      <c r="J34" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K34" s="8" t="s">
@@ -2537,20 +2590,20 @@
     </row>
     <row r="35" spans="2:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="6"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="31"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="29"/>
       <c r="F35" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H35" s="36"/>
-      <c r="I35" s="20" t="s">
+      <c r="H35" s="34"/>
+      <c r="I35" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J35" s="19" t="s">
+      <c r="J35" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K35" s="8" t="s">
@@ -2562,20 +2615,20 @@
     </row>
     <row r="36" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="6"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="32"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="30"/>
       <c r="F36" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H36" s="36"/>
-      <c r="I36" s="20" t="s">
+      <c r="H36" s="34"/>
+      <c r="I36" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J36" s="19" t="s">
+      <c r="J36" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K36" s="8" t="s">
@@ -2587,18 +2640,18 @@
     </row>
     <row r="37" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="6"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="29" t="s">
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F37" s="24" t="s">
+      <c r="F37" s="22" t="s">
         <v>72</v>
       </c>
       <c r="G37" s="2"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
       <c r="K37" s="8" t="s">
         <v>25</v>
       </c>
@@ -2608,39 +2661,39 @@
     </row>
     <row r="38" spans="2:12" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="6"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
       <c r="E38" s="3"/>
       <c r="F38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G38" s="2"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
       <c r="K38" s="8" t="s">
         <v>30</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="6"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H39" s="34" t="s">
+      <c r="H39" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I39" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J39" s="19" t="s">
+      <c r="I39" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J39" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K39" s="12" t="s">
@@ -2652,20 +2705,20 @@
     </row>
     <row r="40" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="6"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H40" s="35" t="s">
+      <c r="H40" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="I40" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J40" s="22" t="s">
+      <c r="I40" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J40" s="21" t="s">
         <v>36</v>
       </c>
       <c r="K40" s="11" t="s">
@@ -2677,20 +2730,20 @@
     </row>
     <row r="41" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="6"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="H41" s="35" t="s">
+      <c r="H41" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="I41" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J41" s="19" t="s">
+      <c r="I41" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J41" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K41" s="8" t="s">
@@ -2702,20 +2755,20 @@
     </row>
     <row r="42" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="6"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H42" s="34" t="s">
+      <c r="H42" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I42" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J42" s="19" t="s">
+      <c r="I42" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J42" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K42" s="8" t="s">
@@ -2727,20 +2780,20 @@
     </row>
     <row r="43" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="6"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H43" s="34" t="s">
+      <c r="H43" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I43" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J43" s="19" t="s">
+      <c r="I43" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J43" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K43" s="12" t="s">
@@ -2752,20 +2805,20 @@
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="6"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="34" t="s">
+      <c r="H44" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I44" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J44" s="19" t="s">
+      <c r="I44" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J44" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K44" s="8" t="s">
@@ -2775,20 +2828,20 @@
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="6"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H45" s="34" t="s">
+      <c r="H45" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I45" s="20" t="s">
+      <c r="I45" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J45" s="19" t="s">
+      <c r="J45" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K45" s="8" t="s">
@@ -2800,20 +2853,20 @@
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="6"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H46" s="35" t="s">
+      <c r="H46" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="I46" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J46" s="19" t="s">
+      <c r="I46" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J46" s="18" t="s">
         <v>36</v>
       </c>
       <c r="K46" s="8" t="s">
@@ -2825,20 +2878,20 @@
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="6"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H47" s="35" t="s">
+      <c r="H47" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="I47" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J47" s="19" t="s">
+      <c r="I47" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J47" s="18" t="s">
         <v>36</v>
       </c>
       <c r="K47" s="8" t="s">
@@ -2850,20 +2903,20 @@
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="6"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="H48" s="35" t="s">
+      <c r="H48" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="I48" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J48" s="19" t="s">
+      <c r="I48" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J48" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K48" s="8" t="s">
@@ -2873,20 +2926,20 @@
     </row>
     <row r="49" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="6"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="H49" s="35">
+      <c r="H49" s="33">
         <v>30</v>
       </c>
-      <c r="I49" s="19" t="s">
+      <c r="I49" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="J49" s="19" t="s">
+      <c r="J49" s="18" t="s">
         <v>84</v>
       </c>
       <c r="K49" s="8" t="s">
@@ -2898,20 +2951,20 @@
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="6"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H50" s="35" t="s">
+      <c r="H50" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="I50" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J50" s="19" t="s">
+      <c r="I50" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J50" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K50" s="8" t="s">
@@ -2923,20 +2976,20 @@
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="6"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
       <c r="E51" s="3"/>
       <c r="F51" s="4"/>
       <c r="G51" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H51" s="35" t="s">
+      <c r="H51" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="I51" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J51" s="19" t="s">
+      <c r="I51" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J51" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K51" s="8" t="s">
@@ -2948,8 +3001,8 @@
     </row>
     <row r="52" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="6"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
       <c r="E52" s="3"/>
       <c r="F52" s="8" t="s">
         <v>18</v>
@@ -2957,11 +3010,11 @@
       <c r="G52" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="H52" s="36"/>
-      <c r="I52" s="20" t="s">
+      <c r="H52" s="34"/>
+      <c r="I52" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J52" s="19" t="s">
+      <c r="J52" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K52" s="8" t="s">
@@ -2973,8 +3026,8 @@
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="6"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
       <c r="E53" s="6"/>
       <c r="F53" s="8" t="s">
         <v>23</v>
@@ -2982,11 +3035,11 @@
       <c r="G53" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H53" s="36"/>
-      <c r="I53" s="20" t="s">
+      <c r="H53" s="34"/>
+      <c r="I53" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J53" s="19" t="s">
+      <c r="J53" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K53" s="8" t="s">
@@ -2998,8 +3051,8 @@
     </row>
     <row r="54" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="6"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
       <c r="E54" s="7"/>
       <c r="F54" s="8" t="s">
         <v>20</v>
@@ -3007,11 +3060,11 @@
       <c r="G54" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H54" s="36"/>
-      <c r="I54" s="20" t="s">
+      <c r="H54" s="34"/>
+      <c r="I54" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J54" s="19" t="s">
+      <c r="J54" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K54" s="8" t="s">
@@ -3023,18 +3076,18 @@
     </row>
     <row r="55" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="6"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="29" t="s">
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="F55" s="24" t="s">
+      <c r="F55" s="22" t="s">
         <v>94</v>
       </c>
       <c r="G55" s="2"/>
-      <c r="H55" s="33"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="18"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17"/>
       <c r="K55" s="8" t="s">
         <v>25</v>
       </c>
@@ -3044,39 +3097,39 @@
     </row>
     <row r="56" spans="2:12" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="6"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
       <c r="E56" s="3"/>
       <c r="F56" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G56" s="2"/>
-      <c r="H56" s="33"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="18"/>
+      <c r="H56" s="31"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
       <c r="K56" s="8" t="s">
         <v>30</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="6"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H57" s="34" t="s">
+      <c r="H57" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I57" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J57" s="19" t="s">
+      <c r="I57" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J57" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K57" s="12" t="s">
@@ -3088,20 +3141,20 @@
     </row>
     <row r="58" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="6"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H58" s="35" t="s">
+      <c r="H58" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="I58" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J58" s="22" t="s">
+      <c r="I58" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J58" s="21" t="s">
         <v>36</v>
       </c>
       <c r="K58" s="11" t="s">
@@ -3113,20 +3166,20 @@
     </row>
     <row r="59" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="6"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="H59" s="35" t="s">
+      <c r="H59" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="I59" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J59" s="19" t="s">
+      <c r="I59" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J59" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K59" s="8" t="s">
@@ -3138,20 +3191,20 @@
     </row>
     <row r="60" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="6"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H60" s="34" t="s">
+      <c r="H60" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I60" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J60" s="19" t="s">
+      <c r="I60" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J60" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K60" s="8" t="s">
@@ -3163,20 +3216,20 @@
     </row>
     <row r="61" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="6"/>
-      <c r="C61" s="17"/>
-      <c r="D61" s="17"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="34" t="s">
+      <c r="H61" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I61" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J61" s="19" t="s">
+      <c r="I61" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J61" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K61" s="12" t="s">
@@ -3188,20 +3241,20 @@
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="6"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H62" s="34" t="s">
+      <c r="H62" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J62" s="19" t="s">
+      <c r="I62" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J62" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K62" s="8" t="s">
@@ -3211,20 +3264,20 @@
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="6"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="17"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H63" s="34" t="s">
+      <c r="H63" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I63" s="20" t="s">
+      <c r="I63" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J63" s="19" t="s">
+      <c r="J63" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K63" s="8" t="s">
@@ -3236,20 +3289,20 @@
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="6"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H64" s="35" t="s">
+      <c r="H64" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="I64" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J64" s="19" t="s">
+      <c r="I64" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J64" s="18" t="s">
         <v>36</v>
       </c>
       <c r="K64" s="8" t="s">
@@ -3261,20 +3314,20 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="6"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="17"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H65" s="35" t="s">
+      <c r="H65" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="I65" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J65" s="19" t="s">
+      <c r="I65" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J65" s="18" t="s">
         <v>36</v>
       </c>
       <c r="K65" s="8" t="s">
@@ -3286,20 +3339,20 @@
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="6"/>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="H66" s="35" t="s">
+      <c r="H66" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="I66" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J66" s="19" t="s">
+      <c r="I66" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J66" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K66" s="8" t="s">
@@ -3309,20 +3362,20 @@
     </row>
     <row r="67" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="6"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="H67" s="35">
+      <c r="H67" s="33">
         <v>30</v>
       </c>
-      <c r="I67" s="19" t="s">
+      <c r="I67" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="J67" s="19" t="s">
+      <c r="J67" s="18" t="s">
         <v>84</v>
       </c>
       <c r="K67" s="8" t="s">
@@ -3334,20 +3387,20 @@
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="6"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H68" s="35" t="s">
+      <c r="H68" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="I68" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J68" s="19" t="s">
+      <c r="I68" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J68" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K68" s="8" t="s">
@@ -3359,20 +3412,20 @@
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="6"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
       <c r="E69" s="3"/>
       <c r="F69" s="4"/>
       <c r="G69" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H69" s="35" t="s">
+      <c r="H69" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="I69" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J69" s="19" t="s">
+      <c r="I69" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J69" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K69" s="8" t="s">
@@ -3384,20 +3437,20 @@
     </row>
     <row r="70" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="6"/>
-      <c r="C70" s="17"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
       <c r="E70" s="3"/>
       <c r="F70" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H70" s="36"/>
-      <c r="I70" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="H70" s="34"/>
+      <c r="I70" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J70" s="19" t="s">
+      <c r="J70" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K70" s="8" t="s">
@@ -3409,8 +3462,8 @@
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="6"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
       <c r="E71" s="6"/>
       <c r="F71" s="8" t="s">
         <v>23</v>
@@ -3418,11 +3471,11 @@
       <c r="G71" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H71" s="36"/>
-      <c r="I71" s="20" t="s">
+      <c r="H71" s="34"/>
+      <c r="I71" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J71" s="19" t="s">
+      <c r="J71" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K71" s="8" t="s">
@@ -3434,8 +3487,8 @@
     </row>
     <row r="72" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="6"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
       <c r="E72" s="7"/>
       <c r="F72" s="8" t="s">
         <v>20</v>
@@ -3443,11 +3496,11 @@
       <c r="G72" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H72" s="36"/>
-      <c r="I72" s="20" t="s">
+      <c r="H72" s="34"/>
+      <c r="I72" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J72" s="19" t="s">
+      <c r="J72" s="18" t="s">
         <v>35</v>
       </c>
       <c r="K72" s="8" t="s">

--- a/マニュアル.xlsx
+++ b/マニュアル.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\7032_川井\SR案件①_20240125\kintone_plugin_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02ED0F4C-CDFE-4AD6-A604-BF7FD6233192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92449AF1-22D0-4E88-804D-5521E75D9FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="18490" windowHeight="11020" xr2:uid="{B4F1298A-2663-45A2-839A-C90A82757019}"/>
   </bookViews>
   <sheets>
-    <sheet name="01.fieldConf" sheetId="1" r:id="rId1"/>
+    <sheet name="基本ルール" sheetId="2" r:id="rId1"/>
+    <sheet name="修正中)イメージ" sheetId="3" r:id="rId2"/>
+    <sheet name="01.fieldConf" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'01.fieldConf'!$A$1:$L$81</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'01.fieldConf'!$A$1:$L$208</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="200">
   <si>
     <t>window</t>
     <phoneticPr fontId="1"/>
@@ -1085,12 +1087,1353 @@
     </r>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>datePicker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓日付</t>
+    <rPh sb="1" eb="3">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>公式サイトのプロパティと同様。※プロパティは省略可能。その場合、初期値が設定される。</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+https://ui-component.kintone.dev/ja/docs/components/desktop/date-picker</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"datePicker"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未指定("")の場合、非表示。初期値を追加したい場合のみ、記載。
+値は、YYYY-MM-DDの通り、設定。
+月/日は省略可能。その場合、01月/01日として設定される。</t>
+    <rPh sb="0" eb="3">
+      <t>ミシテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ヒヒョウジ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ショウリャク</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>checkbox</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓チェックボックス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>items</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>selectedIndex</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>itemLayout</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>borderVisible</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"checkbox"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"select"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>appField</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示する選択肢一覧</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Array&lt;item&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>items = [{label:"", value:""}]
+label：string：各選択肢のテキスト（未指定の場合、valueの値が表示）
+value：string：各選択肢の値
+disabled：boolean：各オプションの選択可/不可設定</t>
+    <rPh sb="54" eb="57">
+      <t>ミシテイ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Array&lt;string&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択されている値</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Array&lt;Number&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択されている値のインデックス番号</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"horizontal"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択肢の並べ方</t>
+    <rPh sb="0" eb="3">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下を指定できる
+"horizontal" : 横並び
+"vertical" : 縦並び</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択肢を囲う枠線の表示/非表示設定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>combobox</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓コンボボックス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"combobox"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Object</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実際に使用しているフィールド情報を選択肢にしたい場合の設定</t>
+    <rPh sb="0" eb="2">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{filter:"",type:[]}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未指定("")の場合、初期値が未選択状態となる。</t>
+    <rPh sb="0" eb="3">
+      <t>ミシテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="15" eb="20">
+      <t>ミセンタクジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>trueの時、表示。falseの時、非表示。未指定の場合、false。
+アイコン表示のみのため、別途入力制御が必要。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>radioButton</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓ラジオボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>appField={filter:"" ,type:[]}
+filter："all"、または"grouped"
+　・all ⇒全てのフィールド情報
+　・grouped ⇒指定したフィールドタイプのみ抽出
+type：[]、または["フィールドタイプ"]
+　・[]⇒filterが"all"の場合、空配列
+　・["SINGLE_LINE_TEXT"]⇒filterが"grouped"の場合、指定するフィールドタイプを配列に追加</t>
+    <rPh sb="63" eb="64">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>チュウシュツ</t>
+    </rPh>
+    <rPh sb="144" eb="146">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="147" eb="150">
+      <t>カラハイレツ</t>
+    </rPh>
+    <rPh sb="191" eb="193">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="194" eb="196">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="207" eb="209">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="210" eb="212">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"radioButton"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するタイプを記載。
+コンボボックスの場合、"combobox"。</t>
+    </r>
+    <rPh sb="33" eb="35">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するカテゴリーを記載。
+コンボボックスの場合、"select"。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するタイプを記載。
+ラジオボタンの場合、"radioButton"。</t>
+    </r>
+    <rPh sb="32" eb="34">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>任意のdiv idを記載。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>必ずhtml内に記載したidと合致する事。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するカテゴリーを記載。
+チェックボックスの場合、"select"。</t>
+    </r>
+    <rPh sb="36" eb="38">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するタイプを記載。
+チェックボックスの場合、"checkbox"。</t>
+    </r>
+    <rPh sb="34" eb="36">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するカテゴリーを記載。
+日付フィールドの場合、"common"。</t>
+    </r>
+    <rPh sb="27" eb="29">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するタイプを記載。
+日付フィールドの場合、"datePicker"。</t>
+    </r>
+    <rPh sb="25" eb="27">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するタイプを記載。
+日時フィールドの場合、"dateTimePicker"。</t>
+    </r>
+    <rPh sb="25" eb="27">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するカテゴリーを記載。
+日時フィールドの場合、"common"。</t>
+    </r>
+    <rPh sb="27" eb="29">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するタイプを記載。
+時刻フィールドの場合、"timePicker"。</t>
+    </r>
+    <rPh sb="25" eb="27">
+      <t>ジコク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するカテゴリーを記載。
+時刻フィールドの場合、"common"。</t>
+    </r>
+    <rPh sb="27" eb="29">
+      <t>ジコク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するタイプを記載。
+テキストエリアの場合、"textarea"。</t>
+    </r>
+    <rPh sb="33" eb="35">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するカテゴリーを記載。
+テキストエリアの場合、"common"。</t>
+    </r>
+    <rPh sb="35" eb="37">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>「別紙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まとめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」シートより、該当するカテゴリーを記載。
+ラジオボタンの場合、"select"。</t>
+    </r>
+    <rPh sb="34" eb="36">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Number</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">value と selectedIndex が未指定の場合、何も選択されない。
+items 内に重複する Item.value がある場合、どの Item.value が選択されるか指定するためのプロパティ。
+value が未指定で、selectedIndex に有効な値が指定されている場合、 そのインデックス番号の選択肢が選択される。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>※value &gt; selectedIndex：value指定ありの時、value指定で選択。</t>
+    </r>
+    <rPh sb="203" eb="204">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="210" eb="212">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="213" eb="215">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">items 内に重複する Item.value がある場合、どの Item.value が選択されるか指定するためのプロパティ。
+value が未指定で、selectedIndex に有効な値が指定されている場合、 そのインデックス番号の選択肢が選択される。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>※value &gt; selectedIndex：value未指定の時、selectedIndex指定で選択。</t>
+    </r>
+    <rPh sb="158" eb="159">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>multiChoice</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓複数選択</t>
+    <rPh sb="1" eb="5">
+      <t>フクスウセンタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"multiChoice"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00.funcConf.js</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01.fieldConf.js</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10.config.js</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●フィールド情報一覧.js
+追加したいフィールド(Kuc)のプロパティ設定。</t>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●設定画面作成用js
+サブテーブルを利用する場合に限り、編集すること。</t>
+    <rPh sb="1" eb="3">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ガメンサクセイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カギ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22行目</t>
+    <rPh sb="2" eb="4">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字列複数行フィールド</t>
+    <rPh sb="0" eb="3">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>フクスウギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>18行目</t>
+    <rPh sb="2" eb="4">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字列一行フィールド</t>
+    <rPh sb="0" eb="3">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23行目</t>
+    <rPh sb="2" eb="4">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時刻フィールド</t>
+    <rPh sb="0" eb="2">
+      <t>ジコク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日時フィールド</t>
+    <rPh sb="0" eb="2">
+      <t>ニチジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付フィールド</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チェックボックスフィールド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>24行目</t>
+    <rPh sb="2" eb="4">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>25行目</t>
+    <rPh sb="2" eb="4">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>26行目</t>
+    <rPh sb="2" eb="4">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>29行目</t>
+    <rPh sb="2" eb="4">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンボボックスフィールド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30行目</t>
+    <rPh sb="2" eb="4">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラジオボタンフィールド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>33行目</t>
+    <rPh sb="2" eb="4">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>複数選択フィールド</t>
+    <rPh sb="0" eb="4">
+      <t>フクスウセンタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34行目</t>
+    <rPh sb="2" eb="4">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dropdown</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドロップダウンフィールド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>38行目</t>
+    <rPh sb="2" eb="4">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>table_sp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブルフィールド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コード行</t>
+    <rPh sb="3" eb="4">
+      <t>ギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●利用者修正箇所　※テーブルは別途ファイル修正が必要</t>
+    <rPh sb="1" eb="4">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>シュウセイカショ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ベット</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修正例</t>
+    <rPh sb="0" eb="2">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>divId = div id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>config.html</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※labelを空文字列ではなく、値を入れれば、フィールド名として表示される</t>
+    <rPh sb="7" eb="8">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（詳細はG列～）</t>
+    <rPh sb="1" eb="3">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>レツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・基本的に以下2ファイルのみ修正が必要。
+⇒01.fieldConf.js、config.html
+・テーブルが必要な場合、10.config.jsに直書きが必要。
+⇒01.fieldConf.jsにも記載が必要。</t>
+    <rPh sb="1" eb="4">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>チョクガ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>●関数一覧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.js</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+基本的に既定値は編集不可。
+ボタン等によるonclick機能を呼び出す関数を記載する場合等に限り、呼び出したい関数を追記。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>※呼び出したい関数は別ファイルにて自ら作成すること。
+※保存したい形式が特殊な場合、setPluginInfo関数内のconfigオブジェクトのconfig.customプロパティに独自の形式で追加すること。
+尚、reflectSavedData()関数(画面反映用関数)へも追記が必要となる。</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>ミズカ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>トクシュ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="126" eb="129">
+      <t>カンスウナイ</t>
+    </rPh>
+    <rPh sb="162" eb="164">
+      <t>ドクジ</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="168" eb="170">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="176" eb="177">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="196" eb="198">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="199" eb="201">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="201" eb="204">
+      <t>ハンエイヨウ</t>
+    </rPh>
+    <rPh sb="204" eb="206">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="209" eb="211">
+      <t>ツイキ</t>
+    </rPh>
+    <rPh sb="212" eb="214">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1193,8 +2536,43 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1210,6 +2588,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1341,7 +2725,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1448,8 +2832,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1467,6 +2893,550 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>440872</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="図 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B803A35E-6588-4A46-B352-E0442939FE5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657225" y="676275"/>
+          <a:ext cx="7622722" cy="6238875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>649968</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>397783</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1193800</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>456580</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="図 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38A14B05-0673-47D2-8F74-3BAE15BBFAF9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="649968" y="11703958"/>
+          <a:ext cx="3464832" cy="4116447"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>67129</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>150132</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1639661</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>172482</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="図 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55E01401-D92C-4CA3-B194-5C8F2BBAC29D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="721179" y="18771507"/>
+          <a:ext cx="3833132" cy="1165350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>524328</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>158844</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="図 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E50D60CF-0061-408D-8AD1-8875FCA211C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12553950" y="706664"/>
+          <a:ext cx="5763078" cy="6322880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="65000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>321625</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>173595</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1705305</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>149555</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="矢印: 右 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B015881-EC3C-4ABC-941C-88A6614D74A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9546443" y="2240231"/>
+          <a:ext cx="2422771" cy="1915597"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>27007</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>108734</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1339643</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>119167</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="正方形/長方形 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A478A94-4C0D-4F07-BBAB-8AE9E729D6C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12542280" y="720643"/>
+          <a:ext cx="1312636" cy="495342"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>633249</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>119166</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>683326</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>397782</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="コネクタ: カギ線 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE2844C1-7B97-4636-81F7-22348F1F217B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="36" idx="2"/>
+          <a:endCxn id="32" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="2804979" y="787618"/>
+          <a:ext cx="9965253" cy="10821986"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 90318"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>40820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1188948</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="図 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5883C142-1F25-47D8-8069-00FC899C3E27}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="647700" y="17233445"/>
+          <a:ext cx="5564098" cy="606880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>48079</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>9528</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>768350</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>144689</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="矢印: 右 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65D8D4C0-EBA4-4BB4-A547-C80BD56143F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="1807484" y="16045998"/>
+          <a:ext cx="706661" cy="726621"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>720271</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>20861</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="矢印: 右 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8C1A90F-101A-47FB-B52A-CC08F68A0D33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="1757817" y="17930358"/>
+          <a:ext cx="706661" cy="717096"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1765,31 +3735,720 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204A08C9-E60C-4A55-B280-58EFBBDD2666}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="4.75" customWidth="1"/>
+    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="89" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+    </row>
+    <row r="2" spans="1:3" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DEB8816-FDDA-468D-A8CE-3CCBD9317977}">
+  <dimension ref="A1:N70"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" customWidth="1"/>
+    <col min="7" max="7" width="6.08203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.58203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="68.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="9.08203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="29" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="47" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="3" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="4" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="5" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="6" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="7" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="8" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="9" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="10" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="11" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="12" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="13" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="14" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="15" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="16" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="17" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="18" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="19" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="20" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="21" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="22" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="23" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="24" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="25" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="26" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="27" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="28" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="29" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="38">
+        <v>1</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="38" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="8">
+        <v>2</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="8">
+        <v>3</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="8">
+        <v>4</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="8">
+        <v>5</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="8">
+        <v>6</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="8">
+        <v>7</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="8">
+        <v>8</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="8">
+        <v>9</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="8">
+        <v>10</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="8">
+        <v>11</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="42" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="43" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="39" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="G45" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="I45" s="2"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="G46" s="28"/>
+      <c r="H46" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46" s="41"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N46" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="G47" s="28"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M47" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="G48" s="28"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L48" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="N48" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="G49" s="28"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="J49" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="K49" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M49" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N49" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G50" s="28"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="J50" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L50" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="N50" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G51" s="28"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="J51" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="K51" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L51" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N51" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G52" s="28"/>
+      <c r="H52" s="42"/>
+      <c r="I52" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="J52" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L52" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M52" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="N52" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="G53" s="28"/>
+      <c r="H53" s="42"/>
+      <c r="I53" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="J53" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="K53" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L53" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="N53" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="G54" s="28"/>
+      <c r="H54" s="42"/>
+      <c r="I54" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="J54" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L54" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M54" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="N54" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="48"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="42"/>
+      <c r="I55" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="J55" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="K55" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L55" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N55" s="8"/>
+    </row>
+    <row r="56" spans="2:14" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E56" t="s">
+        <v>194</v>
+      </c>
+      <c r="G56" s="28"/>
+      <c r="H56" s="42"/>
+      <c r="I56" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="K56" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L56" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="N56" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G57" s="28"/>
+      <c r="H57" s="42"/>
+      <c r="I57" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J57" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="K57" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L57" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="N57" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="G58" s="28"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="J58" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="K58" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L58" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="N58" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="G59" s="28"/>
+      <c r="H59" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J59" s="34"/>
+      <c r="K59" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L59" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N59" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G60" s="29"/>
+      <c r="H60" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J60" s="34"/>
+      <c r="K60" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L60" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N60" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="G61" s="30"/>
+      <c r="H61" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" s="34"/>
+      <c r="K61" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L61" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N61" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="49" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="50" t="s">
+        <v>197</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="N46" r:id="rId1" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{808AA534-7CE8-4443-8B25-ECF8BA706571}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86763921-03DB-411A-87EC-161042BDBDA7}">
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L153"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="3" width="3.9140625" customWidth="1"/>
     <col min="4" max="4" width="5.5" customWidth="1"/>
     <col min="5" max="5" width="20.4140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.4140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="35"/>
+    <col min="8" max="8" width="11.6640625" style="35" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.1640625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="20"/>
+    <col min="10" max="10" width="15.83203125" style="20" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="26.75" customWidth="1"/>
     <col min="12" max="12" width="68.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
       <c r="H1" s="10" t="s">
         <v>74</v>
       </c>
@@ -2585,7 +5244,7 @@
         <v>57</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="2:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
@@ -2635,7 +5294,7 @@
         <v>62</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -3021,7 +5680,7 @@
         <v>57</v>
       </c>
       <c r="L52" s="12" t="s">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -3071,7 +5730,7 @@
         <v>62</v>
       </c>
       <c r="L54" s="12" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -3457,7 +6116,7 @@
         <v>57</v>
       </c>
       <c r="L70" s="12" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -3507,7 +6166,1966 @@
         <v>62</v>
       </c>
       <c r="L72" s="12" t="s">
-        <v>61</v>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="6"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F73" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="G73" s="2"/>
+      <c r="H73" s="31"/>
+      <c r="I73" s="17"/>
+      <c r="J73" s="17"/>
+      <c r="K73" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L73" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="6"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G74" s="2"/>
+      <c r="H74" s="31"/>
+      <c r="I74" s="17"/>
+      <c r="J74" s="17"/>
+      <c r="K74" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L74" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="6"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H75" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I75" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J75" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K75" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L75" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="6"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H76" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J76" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L76" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="6"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H77" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I77" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J77" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K77" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L77" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="6"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H78" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I78" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K78" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L78" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="6"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H79" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I79" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J79" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K79" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L79" s="8"/>
+    </row>
+    <row r="80" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="6"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H80" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I80" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J80" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K80" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L80" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="6"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J81" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K81" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L81" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="6"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J82" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K82" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L82" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="6"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H83" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="I83" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J83" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K83" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L83" s="12"/>
+    </row>
+    <row r="84" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="6"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H84" s="34"/>
+      <c r="I84" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J84" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K84" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L84" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="6"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H85" s="34"/>
+      <c r="I85" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J85" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K85" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="86" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="6"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H86" s="34"/>
+      <c r="I86" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J86" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K86" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L86" s="12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="87" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" s="6"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F87" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G87" s="2"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="17"/>
+      <c r="J87" s="17"/>
+      <c r="K87" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L87" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="88" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="6"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G88" s="2"/>
+      <c r="H88" s="31"/>
+      <c r="I88" s="17"/>
+      <c r="J88" s="17"/>
+      <c r="K88" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L88" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" s="6"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I89" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J89" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K89" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L89" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="90" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" s="6"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H90" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I90" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J90" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="K90" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L90" s="14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="91" spans="2:12" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" s="6"/>
+      <c r="C91" s="16"/>
+      <c r="D91" s="16"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H91" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="I91" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J91" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="K91" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L91" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="92" spans="2:12" ht="108" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" s="6"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H92" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="I92" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J92" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="K92" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="L92" s="12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="93" spans="2:12" ht="90" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" s="6"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="16"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H93" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="I93" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J93" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K93" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="L93" s="12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="94" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" s="6"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="16"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H94" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="I94" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J94" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K94" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L94" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="95" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" s="6"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="16"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H95" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I95" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J95" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K95" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L95" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="96" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" s="6"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H96" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J96" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K96" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L96" s="12"/>
+    </row>
+    <row r="97" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" s="6"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I97" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J97" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K97" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L97" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="98" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" s="6"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="16"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H98" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I98" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J98" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K98" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L98" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="99" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" s="6"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I99" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J99" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K99" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L99" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="100" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" s="6"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H100" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J100" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K100" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="L100" s="12"/>
+    </row>
+    <row r="101" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" s="6"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H101" s="34"/>
+      <c r="I101" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J101" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K101" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L101" s="12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="102" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" s="6"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H102" s="34"/>
+      <c r="I102" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J102" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K102" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L102" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="103" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" s="6"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H103" s="34"/>
+      <c r="I103" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J103" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K103" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L103" s="12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="104" spans="2:12" ht="162" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B104" s="6"/>
+      <c r="C104" s="16"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="H104" s="34"/>
+      <c r="I104" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="J104" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="K104" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="L104" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="105" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B105" s="6"/>
+      <c r="C105" s="16"/>
+      <c r="D105" s="16"/>
+      <c r="E105" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F105" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G105" s="2"/>
+      <c r="H105" s="31"/>
+      <c r="I105" s="17"/>
+      <c r="J105" s="17"/>
+      <c r="K105" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L105" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="106" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B106" s="6"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G106" s="2"/>
+      <c r="H106" s="31"/>
+      <c r="I106" s="17"/>
+      <c r="J106" s="17"/>
+      <c r="K106" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L106" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" s="6"/>
+      <c r="C107" s="16"/>
+      <c r="D107" s="16"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H107" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I107" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J107" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K107" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L107" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="108" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B108" s="6"/>
+      <c r="C108" s="16"/>
+      <c r="D108" s="16"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H108" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I108" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J108" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="K108" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L108" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="109" spans="2:12" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" s="6"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H109" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="I109" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J109" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="K109" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L109" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="110" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" s="6"/>
+      <c r="C110" s="16"/>
+      <c r="D110" s="16"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H110" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I110" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J110" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K110" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="L110" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="111" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B111" s="6"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H111" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I111" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J111" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K111" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L111" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="112" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" s="6"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H112" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I112" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J112" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K112" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L112" s="12"/>
+    </row>
+    <row r="113" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B113" s="6"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H113" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I113" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J113" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K113" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="114" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B114" s="6"/>
+      <c r="C114" s="16"/>
+      <c r="D114" s="16"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H114" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J114" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K114" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L114" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="115" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" s="6"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I115" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J115" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K115" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L115" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="116" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B116" s="6"/>
+      <c r="C116" s="16"/>
+      <c r="D116" s="16"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="H116" s="34"/>
+      <c r="I116" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J116" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K116" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L116" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="117" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B117" s="6"/>
+      <c r="C117" s="16"/>
+      <c r="D117" s="16"/>
+      <c r="E117" s="6"/>
+      <c r="F117" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H117" s="34"/>
+      <c r="I117" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J117" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K117" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L117" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="118" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B118" s="6"/>
+      <c r="C118" s="16"/>
+      <c r="D118" s="16"/>
+      <c r="E118" s="6"/>
+      <c r="F118" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H118" s="34"/>
+      <c r="I118" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J118" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K118" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L118" s="12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="119" spans="2:12" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="B119" s="6"/>
+      <c r="C119" s="16"/>
+      <c r="D119" s="16"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="H119" s="34"/>
+      <c r="I119" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="J119" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="K119" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="L119" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="120" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B120" s="6"/>
+      <c r="C120" s="16"/>
+      <c r="D120" s="16"/>
+      <c r="E120" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="F120" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="G120" s="2"/>
+      <c r="H120" s="31"/>
+      <c r="I120" s="17"/>
+      <c r="J120" s="17"/>
+      <c r="K120" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L120" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B121" s="6"/>
+      <c r="C121" s="16"/>
+      <c r="D121" s="16"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G121" s="2"/>
+      <c r="H121" s="31"/>
+      <c r="I121" s="17"/>
+      <c r="J121" s="17"/>
+      <c r="K121" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L121" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="122" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B122" s="6"/>
+      <c r="C122" s="16"/>
+      <c r="D122" s="16"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H122" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I122" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J122" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K122" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L122" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="123" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B123" s="6"/>
+      <c r="C123" s="16"/>
+      <c r="D123" s="16"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H123" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I123" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J123" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="K123" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L123" s="14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="124" spans="2:12" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="B124" s="6"/>
+      <c r="C124" s="16"/>
+      <c r="D124" s="16"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H124" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="I124" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J124" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="K124" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L124" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="125" spans="2:12" ht="108" x14ac:dyDescent="0.55000000000000004">
+      <c r="B125" s="6"/>
+      <c r="C125" s="16"/>
+      <c r="D125" s="16"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H125" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I125" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J125" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K125" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="L125" s="12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="126" spans="2:12" ht="90" x14ac:dyDescent="0.55000000000000004">
+      <c r="B126" s="6"/>
+      <c r="C126" s="16"/>
+      <c r="D126" s="16"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H126" s="32">
+        <v>-1</v>
+      </c>
+      <c r="I126" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J126" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="K126" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="L126" s="12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="127" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B127" s="6"/>
+      <c r="C127" s="16"/>
+      <c r="D127" s="16"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H127" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="I127" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J127" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K127" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L127" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B128" s="6"/>
+      <c r="C128" s="16"/>
+      <c r="D128" s="16"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H128" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I128" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J128" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K128" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L128" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="129" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B129" s="6"/>
+      <c r="C129" s="16"/>
+      <c r="D129" s="16"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H129" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I129" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J129" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K129" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L129" s="12"/>
+    </row>
+    <row r="130" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B130" s="6"/>
+      <c r="C130" s="16"/>
+      <c r="D130" s="16"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H130" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I130" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J130" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K130" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L130" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="131" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B131" s="6"/>
+      <c r="C131" s="16"/>
+      <c r="D131" s="16"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H131" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I131" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J131" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K131" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L131" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="132" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B132" s="6"/>
+      <c r="C132" s="16"/>
+      <c r="D132" s="16"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I132" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J132" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K132" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L132" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="133" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B133" s="6"/>
+      <c r="C133" s="16"/>
+      <c r="D133" s="16"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H133" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J133" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K133" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="L133" s="12"/>
+    </row>
+    <row r="134" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B134" s="6"/>
+      <c r="C134" s="16"/>
+      <c r="D134" s="16"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="H134" s="34"/>
+      <c r="I134" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J134" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K134" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L134" s="12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="135" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B135" s="6"/>
+      <c r="C135" s="16"/>
+      <c r="D135" s="16"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H135" s="34"/>
+      <c r="I135" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J135" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K135" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L135" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="136" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B136" s="6"/>
+      <c r="C136" s="16"/>
+      <c r="D136" s="16"/>
+      <c r="E136" s="6"/>
+      <c r="F136" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H136" s="34"/>
+      <c r="I136" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J136" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K136" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L136" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="137" spans="2:12" ht="162" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B137" s="6"/>
+      <c r="C137" s="16"/>
+      <c r="D137" s="16"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="H137" s="34"/>
+      <c r="I137" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="J137" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="K137" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="L137" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="138" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B138" s="6"/>
+      <c r="C138" s="16"/>
+      <c r="D138" s="16"/>
+      <c r="E138" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="F138" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="G138" s="2"/>
+      <c r="H138" s="31"/>
+      <c r="I138" s="17"/>
+      <c r="J138" s="17"/>
+      <c r="K138" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L138" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="139" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B139" s="6"/>
+      <c r="C139" s="16"/>
+      <c r="D139" s="16"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G139" s="2"/>
+      <c r="H139" s="31"/>
+      <c r="I139" s="17"/>
+      <c r="J139" s="17"/>
+      <c r="K139" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L139" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="140" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B140" s="6"/>
+      <c r="C140" s="16"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H140" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I140" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J140" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K140" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L140" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="141" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B141" s="6"/>
+      <c r="C141" s="16"/>
+      <c r="D141" s="16"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H141" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I141" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J141" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="K141" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L141" s="14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="142" spans="2:12" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="B142" s="6"/>
+      <c r="C142" s="16"/>
+      <c r="D142" s="16"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H142" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="I142" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J142" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="K142" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L142" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="143" spans="2:12" ht="108" x14ac:dyDescent="0.55000000000000004">
+      <c r="B143" s="6"/>
+      <c r="C143" s="16"/>
+      <c r="D143" s="16"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H143" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="I143" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J143" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="K143" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="L143" s="12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="144" spans="2:12" ht="90" x14ac:dyDescent="0.55000000000000004">
+      <c r="B144" s="6"/>
+      <c r="C144" s="16"/>
+      <c r="D144" s="16"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H144" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="I144" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J144" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K144" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="L144" s="12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="145" spans="2:12" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B145" s="6"/>
+      <c r="C145" s="16"/>
+      <c r="D145" s="16"/>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H145" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I145" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J145" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K145" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L145" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="146" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B146" s="6"/>
+      <c r="C146" s="16"/>
+      <c r="D146" s="16"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H146" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I146" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J146" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K146" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L146" s="12"/>
+    </row>
+    <row r="147" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B147" s="6"/>
+      <c r="C147" s="16"/>
+      <c r="D147" s="16"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H147" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I147" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J147" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K147" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L147" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="148" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B148" s="6"/>
+      <c r="C148" s="16"/>
+      <c r="D148" s="16"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3"/>
+      <c r="G148" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H148" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J148" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K148" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L148" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="149" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B149" s="6"/>
+      <c r="C149" s="16"/>
+      <c r="D149" s="16"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H149" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I149" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J149" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K149" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L149" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="150" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B150" s="6"/>
+      <c r="C150" s="16"/>
+      <c r="D150" s="16"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="H150" s="34"/>
+      <c r="I150" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J150" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K150" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L150" s="12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="151" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="B151" s="6"/>
+      <c r="C151" s="16"/>
+      <c r="D151" s="16"/>
+      <c r="E151" s="6"/>
+      <c r="F151" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H151" s="34"/>
+      <c r="I151" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J151" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K151" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L151" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="152" spans="2:12" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B152" s="6"/>
+      <c r="C152" s="16"/>
+      <c r="D152" s="16"/>
+      <c r="E152" s="6"/>
+      <c r="F152" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H152" s="34"/>
+      <c r="I152" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J152" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K152" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L152" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="153" spans="2:12" ht="162" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B153" s="6"/>
+      <c r="C153" s="16"/>
+      <c r="D153" s="16"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="H153" s="34"/>
+      <c r="I153" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="J153" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="K153" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="L153" s="12" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -3520,8 +8138,13 @@
     <hyperlink ref="L24" r:id="rId2" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{4E3AB564-235F-4DAA-AB2E-0A796A8F14FF}"/>
     <hyperlink ref="L38" r:id="rId3" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{A5F7688D-101F-4607-9B37-CE23A225ADB1}"/>
     <hyperlink ref="L56" r:id="rId4" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{6DF4276D-B532-4201-8152-E3F4BA2FAC53}"/>
+    <hyperlink ref="L74" r:id="rId5" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{47FA82FD-D202-4F3D-A988-23A47300FE7A}"/>
+    <hyperlink ref="L88" r:id="rId6" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{E2F1C3C5-E48A-46EC-8DF0-4404BBA597E0}"/>
+    <hyperlink ref="L106" r:id="rId7" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{4CAC22A1-51E6-4E92-9FF0-A1BC70B3CC84}"/>
+    <hyperlink ref="L121" r:id="rId8" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{B746FA34-866B-4207-8707-AE4C485E3D06}"/>
+    <hyperlink ref="L139" r:id="rId9" location="property" display="https://ui-component.kintone.dev/ja/docs/components/desktop/text#property" xr:uid="{EBF30F29-9489-4F1A-9B57-EE568C7B3A4E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="12" scale="61" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="12" scale="56" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>